--- a/01_경혈별_해부생리_분석보고서/GB_족소양담경/GB39_현종/GB39_현종_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/GB_족소양담경/GB39_현종/GB39_현종_해부생리_분석데이터.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2775,7 +2776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2939,7 +2940,103 @@
       <c r="F5" t="n">
         <v>27</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:43:36</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pubmed</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>("GB39" OR "Xuanzhong" OR "悬钟") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy) | ("GB39" OR "Xuanzhong" OR "悬钟") AND ("Zhongguo Zhen Jiu"[Journal] OR "Zhen Ci Yan Jiu"[Journal])</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:43:36</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>doi_starts_with:10.13703,title_and_abstract.search:"Xuanzhong" OR "GB39" | doi_starts_with:10.13702,title_and_abstract.search:"Xuanzhong" OR "GB39" | has_doi:true,title_and_abstract.search:"Xuanzhong" OR "GB39" AND (acupuncture OR electroacupuncture)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:43:36</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>crossref</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Xuanzhong acupuncture nerve reflex</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:43:36</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>40</v>
+      </c>
+      <c r="E9" t="n">
+        <v>33</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2952,7 +3049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3392,6 +3489,757 @@
       <c r="D20" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가. T1 ARI-Core 51.2 ± 0 (D·H)·T2 55.0 ± 0 (C) 불변</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>fma_query.py profile GB39; 보고서 4·6·8절·부록 A</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>교재 용어</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FMA_ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FMA_label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>대응 수준</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>출처 교재</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>지배신경(FMA nerve_supply)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>상위 줄기(FMA)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>척수 분절(FMA segmental_supply)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>긴발가락폄근 (extensor digitorum longus)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>22534</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Extensor digitorum longus</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FMA:80068 Nerve to extensor digitorum longus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Medial terminal branch of deep fibular nerve → Deep fibular nerve → Common fibular nerve → Sciatic nerve → Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>L5(primary/segmental), S1(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>근육가지 기원: FMA는 안쪽종말가지로 기록 → 깊은종아리신경 수준만 인용</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>긴엄지폄근 (extensor hallucis longus)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>22533</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Extensor hallucis longus</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FMA:80065 Nerve to extensor hallucis longus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Medial terminal branch of deep fibular nerve → Deep fibular nerve → Common fibular nerve → Sciatic nerve → Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>L5(primary/segmental), S1(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>위와 같음</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>짧은종아리근 (fibularis brevis); 짧은종아리근 (peroneus brevis)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>22540</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Fibularis brevis</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FMA:80082 Nerve to fibularis brevis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Superficial fibular nerve → Common fibular nerve → Sciatic nerve → Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>L5(segmental), S1(segmental)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>긴종아리근 (peroneus longus)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>22539</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fibularis longus</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FMA:80079 Nerve to fibularis longus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Superficial fibular nerve → Common fibular nerve → Sciatic nerve → Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>L4(segmental), L5(segmental), S1(segmental)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>셋째종아리근 (fibularis tertius)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>22538</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Fibularis tertius</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FMA:80071 Nerve to fibularis tertius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Medial terminal branch of deep fibular nerve → Deep fibular nerve → Common fibular nerve → Sciatic nerve → Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>L5(segmental), S1(segmental)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>위와 같음</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>긴엄지굽힘근 (flexor hallucis longus)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>22593</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Flexor hallucis longus</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FMA:80098 Nerve to flexor hallucis longus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Tibial nerve → Sciatic nerve → Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>S1(primary/segmental), S2(primary/segmental), L5(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>뒤칸 깊은층(FMA:312109)·정강신경 — 김재효 단독</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>깊은종아리신경 (deep fibular nerve); 깊은종아리신경 (deep peroneal nerve)</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>44771</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Deep fibular nerve</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>FMA:19039 Common fibular nerve → FMA:19034 Sciatic nerve → FMA:5909 Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>가쪽장딴지피부신경 (lateral sural cutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>44697</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Lateral sural cutaneous nerve</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>FMA:19039 Common fibular nerve → FMA:19034 Sciatic nerve → FMA:5909 Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>얕은종아리신경 (superficial fibular nerve); 얕은종아리신경 (superficial peroneal nerve)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>44699</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Superficial fibular nerve</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>FMA:19039 Common fibular nerve → FMA:19034 Sciatic nerve → FMA:5909 Sacral nerve plexus</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>앞정강동ㆍ정맥 (anterior tibial artery and vein)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>43894</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Anterior tibial artery</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FMA:18805 External iliac artery → FMA:14764 Common iliac artery</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>FMA는 오금동맥을 바깥엉덩동맥 연속 구간으로 모델링</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>앞정강동ㆍ정맥 (anterior tibial artery and vein)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>44331</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Anterior tibial vein</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>FMA:44327 Popliteal vein → FMA:51041 Deep femoral vein → FMA:21185 Femoral vein → FMA:18883 External iliac vein → FMA:14333 Common iliac vein → FMA:10951 Inferior vena cava</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>종아리동ㆍ정맥 (fibular artery and vein)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>44558</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fibular vein</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>FMA:44327 Popliteal vein → FMA:51041 Deep femoral vein → FMA:21185 Femoral vein → FMA:18883 External iliac vein → FMA:14333 Common iliac vein → FMA:10951 Inferior vena cava</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FMA drains_into Femoral vein — 규범 해부와 다름, 인용 안 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>종아리동맥의 관통가지 (perforating branch of the fibular artery)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>44033</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Perforating branch of fibular artery</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>FMA:43921 Peroneal artery</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>종아리동ㆍ정맥 (fibular artery and vein)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>43921</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Peroneal artery</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>분절 합집합</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>L4, L5, S1, S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>교재 비교</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>공통 7 · 공통교재 단독 1 · 김재효 단독 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 로컬 색인, fma_query.py profile GB39 (2026-10-23). B1 보조(등록부 미등재)</t>
         </is>
       </c>
     </row>
@@ -5092,10 +5940,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A23:G23"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11052,8 +11900,6 @@
       <c r="E6" t="n">
         <v>75</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11075,8 +11921,6 @@
       <c r="E7" t="n">
         <v>50</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11098,8 +11942,6 @@
       <c r="E8" t="n">
         <v>75</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11121,8 +11963,6 @@
       <c r="E9" t="n">
         <v>75</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11268,8 +12108,6 @@
       <c r="E14" t="n">
         <v>75</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11291,8 +12129,6 @@
       <c r="E15" t="n">
         <v>50</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11314,8 +12150,6 @@
       <c r="E16" t="n">
         <v>50</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11337,8 +12171,6 @@
       <c r="E17" t="n">
         <v>75</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="65" t="inlineStr">
@@ -11665,7 +12497,6 @@
           <t>B1-03, B3-05</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>깊은종아리신경 L4~L5(S1) 근절·피절 vs 《明堂》 원주치 표적(위, T6~T9 내장절) 분절 불일치. 하지 자극의 위운동 조절은 상척수성(미주) 체성-자율 반사로 설명되는 유추 수준 → 1.</t>
@@ -11817,7 +12648,6 @@
           <t>B4-05</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>T1 위치 자침의 인체 신경영상·자율신경 지표·임상 연구 없음. 혈위 특이성 논쟁(B4-05) 미해결 → 0.</t>
@@ -11849,14 +12679,11 @@
       <c r="E8" t="n">
         <v>5</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>미부합 → 반사 기전 가설</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11881,7 +12708,6 @@
           <t>B1-01, B1-03, B2-09</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>얕은·깊은종아리신경, 앞정강동정맥, 폄근군은 규범 해부·2대 교재로 확인되나 GB39 특이 영상·사체 실측 논문 없음(B2 2점 조건 미충족). 보고서의 '비골동맥 관통지=動脈中' 주장은 《通考》의 앞정강동맥 해석과 불일치.</t>
@@ -11916,7 +12742,6 @@
           <t>B1-03, B3-05, B3-20</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>L4~S1 피절·근절은 국소 주치(下肢痿痺·足脛痛)와 정합. 보고서의 'L4-S1→C3-C5 체성-체성 이완 반사'(頸項强痛)는 분절 근거 없음. 명당경 원주치(위병, T6~T9)와도 분절 불일치.</t>
@@ -12104,14 +12929,11 @@
       <c r="E15" t="n">
         <v>6</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>미부합 → 반사 기전 가설</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12186,7 +13008,6 @@
           <t>关于悬钟穴定位的探讨 / Location of acupoint Xuanzhong (GB39) — 刘佳男 등</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>10.13702/j.1000-0607.200282 (본문 PDF)</t>
@@ -12220,8 +13041,6 @@
           <t>치매와 관련된 뇌영역에 투사되는 경혈(SJ5·PC6·SP6·GB39)의 신경해부학적 연구</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>동물 신경추적</t>
@@ -12250,8 +13069,6 @@
           <t>양릉천-현종 전침치료가 뇌경색환자 및 정상인의 뇌혈류에 미치는 영향</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>인체 비RCT(배혈)</t>
@@ -12280,7 +13097,6 @@
           <t>懸鍾(GB39)·陽陵泉(GB34)의 電鍼 및 레이저침이 白鼠의 神經病理性 疼痛에 미치는 영향</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>10.13045/acupunct.2013012</t>
@@ -12428,8 +13244,6 @@
           <t>髓会绝骨的文献研究及临床应用概论</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>문헌 연구</t>

--- a/01_경혈별_해부생리_분석보고서/GB_족소양담경/GB39_현종/GB39_현종_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/GB_족소양담경/GB39_현종/GB39_현종_해부생리_분석데이터.xlsx
@@ -14,11 +14,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet5_해부학적실체" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구판_Sheet6_ARI평가" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARI_v3.0" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-Check" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기추론_TriTarget" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-Check" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -314,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -503,6 +504,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -868,7 +882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2751,6 +2765,494 @@
       <c r="J90" s="2" t="n"/>
       <c r="K90" s="2" t="n"/>
       <c r="L90" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="66" t="inlineStr">
+        <is>
+          <t>【2026-10-25 Framework 2.7.7】 4대 원전 확장 — 《中国针灸经络通鉴》 교감 및 《证治通鉴》 포인터 갱신 (내부 포인터: 파일·행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="67" t="inlineStr">
+        <is>
+          <t>원전</t>
+        </is>
+      </c>
+      <c r="B93" s="67" t="inlineStr">
+        <is>
+          <t>편·인용 문헌</t>
+        </is>
+      </c>
+      <c r="C93" s="67" t="inlineStr">
+        <is>
+          <t>파일 (내부 포인터)</t>
+        </is>
+      </c>
+      <c r="D93" s="67" t="inlineStr">
+        <is>
+          <t>행</t>
+        </is>
+      </c>
+      <c r="E93" s="67" t="inlineStr">
+        <is>
+          <t>원문 발췌</t>
+        </is>
+      </c>
+      <c r="F93" s="67" t="inlineStr">
+        <is>
+          <t>판정·비고</t>
+        </is>
+      </c>
+      <c r="G93" s="67" t="inlineStr">
+        <is>
+          <t>보고서 위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="68" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B94" s="68" t="inlineStr">
+        <is>
+          <t>01편 第壹编 第一篇 五.古人对经脉、络脉实质的认识</t>
+        </is>
+      </c>
+      <c r="C94" s="68" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md</t>
+        </is>
+      </c>
+      <c r="D94" s="68" t="inlineStr">
+        <is>
+          <t>L2007–2017</t>
+        </is>
+      </c>
+      <c r="E94" s="68" t="inlineStr">
+        <is>
+          <t>悬钟穴：足三阳络，按之阳明脉绝乃取之（《明堂经》）… 这里所谓"阳明脉"即王冰所说的"足跗上动脉"，也即足背动脉，由于它是胫前动脉的下行支，故于位于胫前动脉之上方的"悬钟"、"足三里"穴处用力按压，则于足背当"冲阳脉"处摸不到足背动脉的搏动</t>
+        </is>
+      </c>
+      <c r="F94" s="68" t="inlineStr">
+        <is>
+          <t>Target 1≡2(앞정강동맥 맥동점) 실체 해석 지지; S_orig④ 단계 이동 없음</t>
+        </is>
+      </c>
+      <c r="G94" s="68" t="inlineStr">
+        <is>
+          <t>1절·7절·10절</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="68" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B95" s="68" t="inlineStr">
+        <is>
+          <t>01편 《明堂经》 刺疟方 按</t>
+        </is>
+      </c>
+      <c r="C95" s="68" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md</t>
+        </is>
+      </c>
+      <c r="D95" s="68" t="inlineStr">
+        <is>
+          <t>L1033–1035</t>
+        </is>
+      </c>
+      <c r="E95" s="68" t="inlineStr">
+        <is>
+          <t>"绝骨"穴不见于《明堂经》，后世医家或以之为悬钟穴，或以之为阳辅穴。敦煌卷子医方（编号：P.3596）… 古代医书中此二穴多有混淆，应注意鉴别</t>
+        </is>
+      </c>
+      <c r="F95" s="68" t="inlineStr">
+        <is>
+          <t>絶骨 혼동(Rank 3); 사본 번호 P.3596 — 证治通鉴 03편은 S.3347(이문)</t>
+        </is>
+      </c>
+      <c r="G95" s="68" t="inlineStr">
+        <is>
+          <t>1·2·3절</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="68" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B96" s="68" t="inlineStr">
+        <is>
+          <t>04편 经络学说的演变 — 王冰 《刺腰痛》 注 및 按</t>
+        </is>
+      </c>
+      <c r="C96" s="68" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/中国针灸经络通鉴_04_第壹编_第二篇_经络学说的演变(十二~十三).md</t>
+        </is>
+      </c>
+      <c r="D96" s="68" t="inlineStr">
+        <is>
+          <t>L1016–1018</t>
+        </is>
+      </c>
+      <c r="E96" s="68" t="inlineStr">
+        <is>
+          <t>绝骨之前，足少阳脉所行；绝骨之后，阳维脉所过 / 按: … 是宋以后医家根据腧穴文献中维脉交会穴部位推测而来</t>
+        </is>
+      </c>
+      <c r="F96" s="68" t="inlineStr">
+        <is>
+          <t>경락론적 확장 비판(혈위 위치 → 경맥 순행 역추정)</t>
+        </is>
+      </c>
+      <c r="G96" s="68" t="inlineStr">
+        <is>
+          <t>1·3절 Rank 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="68" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B97" s="68" t="inlineStr">
+        <is>
+          <t>36편 其他脉 — 王冰 注 "传写误", 按</t>
+        </is>
+      </c>
+      <c r="C97" s="68" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/中国针灸经络通鉴_36_第肆编_第七篇_其他脉.md</t>
+        </is>
+      </c>
+      <c r="D97" s="68" t="inlineStr">
+        <is>
+          <t>L193, L197–199, L209</t>
+        </is>
+      </c>
+      <c r="E97" s="68" t="inlineStr">
+        <is>
+          <t>一经云少阳绝骨之前，传写误也 … / 按：阳辅穴在绝骨之前，非其后也 … 后世注家不察王注，不考《明堂》，视"阳辅"、"分肉"为同一穴</t>
+        </is>
+      </c>
+      <c r="F97" s="68" t="inlineStr">
+        <is>
+          <t>필사 오류 감별(王冰 판정), 阳辅·分肉 혼동 비판</t>
+        </is>
+      </c>
+      <c r="G97" s="68" t="inlineStr">
+        <is>
+          <t>1·2·3절 Rank 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="68" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B98" s="68" t="inlineStr">
+        <is>
+          <t>05편 L760, 28편 L1092, 36편 L265·271</t>
+        </is>
+      </c>
+      <c r="C98" s="68" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/…_05_… / …_28_… / …_36_…</t>
+        </is>
+      </c>
+      <c r="D98" s="68" t="inlineStr">
+        <is>
+          <t>L760; L1092; L265, L271</t>
+        </is>
+      </c>
+      <c r="E98" s="68" t="inlineStr">
+        <is>
+          <t>直上抵绝骨之端 / 下外辅骨之前，下抵绝骨 / 同阴之脉 … 在外踝上绝骨之端(杨注 当是足少阳络脉)</t>
+        </is>
+      </c>
+      <c r="F98" s="68" t="inlineStr">
+        <is>
+          <t>绝骨 = 골성 지표(Target 3 계통 정위의 경맥 근거)</t>
+        </is>
+      </c>
+      <c r="G98" s="68" t="inlineStr">
+        <is>
+          <t>1절·7절</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="68" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B99" s="68" t="inlineStr">
+        <is>
+          <t>34편 L414, 35편 L365, 11편 L845</t>
+        </is>
+      </c>
+      <c r="C99" s="68" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/…_34_… / …_35_… / …_11_…</t>
+        </is>
+      </c>
+      <c r="D99" s="68" t="inlineStr">
+        <is>
+          <t>L414; L365; L845</t>
+        </is>
+      </c>
+      <c r="E99" s="68" t="inlineStr">
+        <is>
+          <t>直取阳跷，在外踝上三寸直绝骨是 / 在外踝绝骨下二寸 / 髓会绝骨</t>
+        </is>
+      </c>
+      <c r="F99" s="68" t="inlineStr">
+        <is>
+          <t>다른 계통 자침처·八会 이론(현종 정위 기술 아님)</t>
+        </is>
+      </c>
+      <c r="G99" s="68" t="inlineStr">
+        <is>
+          <t>1절</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="68" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴</t>
+        </is>
+      </c>
+      <c r="B100" s="68" t="inlineStr">
+        <is>
+          <t>28편 足少阳 경혈 목록</t>
+        </is>
+      </c>
+      <c r="C100" s="68" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸经络通鉴/中国针灸经络通鉴_28_第叁编_第十一篇_足少阳经脉、经别、络脉和经筋.md</t>
+        </is>
+      </c>
+      <c r="D100" s="68" t="inlineStr">
+        <is>
+          <t>L331, L343, L351</t>
+        </is>
+      </c>
+      <c r="E100" s="68" t="inlineStr">
+        <is>
+          <t>… 丘墟 … 悬钟 … 阳辅 …</t>
+        </is>
+      </c>
+      <c r="F100" s="68" t="inlineStr">
+        <is>
+          <t>목록 수록뿐 — 현종 정위 문구 교감 없음</t>
+        </is>
+      </c>
+      <c r="G100" s="68" t="inlineStr">
+        <is>
+          <t>1절</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="68" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴</t>
+        </is>
+      </c>
+      <c r="B101" s="68" t="inlineStr">
+        <is>
+          <t>09편 足少阳胆经 二十)悬钟 (원문)</t>
+        </is>
+      </c>
+      <c r="C101" s="68" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸证治通鉴/中国针灸证治通鉴_09_第壹编_第七篇_足少阳胆经_足厥阴肝经.md</t>
+        </is>
+      </c>
+      <c r="D101" s="68" t="inlineStr">
+        <is>
+          <t>L426–458</t>
+        </is>
+      </c>
+      <c r="E101" s="68" t="inlineStr">
+        <is>
+          <t>主腹满，胃中有热，不嗜食。小儿腹满，不能食饮。… 小结：隋唐时，阳辅穴又名绝骨，与悬钟穴多相混</t>
+        </is>
+      </c>
+      <c r="F101" s="68" t="inlineStr">
+        <is>
+          <t>한글번역 L568–608</t>
+        </is>
+      </c>
+      <c r="G101" s="68" t="inlineStr">
+        <is>
+          <t>1절</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="68" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴</t>
+        </is>
+      </c>
+      <c r="B102" s="68" t="inlineStr">
+        <is>
+          <t>17편 《针灸聚英·杂病十一穴歌》</t>
+        </is>
+      </c>
+      <c r="C102" s="68" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸证治通鉴/中国针灸证治通鉴_17_第叁编_内科病症_二十二脏腑病证至二十四胸胁满痛.md</t>
+        </is>
+      </c>
+      <c r="D102" s="68" t="inlineStr">
+        <is>
+          <t>L406 (한글번역 L655–657)</t>
+        </is>
+      </c>
+      <c r="E102" s="68" t="inlineStr">
+        <is>
+          <t>乃若胃热治悬钟</t>
+        </is>
+      </c>
+      <c r="F102" s="68" t="inlineStr">
+        <is>
+          <t>구 포인터 "PDF 161–240쪽 L4132" 대체</t>
+        </is>
+      </c>
+      <c r="G102" s="68" t="inlineStr">
+        <is>
+          <t>1절</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="68" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴</t>
+        </is>
+      </c>
+      <c r="B103" s="68" t="inlineStr">
+        <is>
+          <t>19편 腹满不食</t>
+        </is>
+      </c>
+      <c r="C103" s="68" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸证治通鉴/中国针灸证治通鉴_19_第叁编_内科病症_三十一腹痛至三十八泄痢.md</t>
+        </is>
+      </c>
+      <c r="D103" s="68" t="inlineStr">
+        <is>
+          <t>L442 (한글번역 L717–719)</t>
+        </is>
+      </c>
+      <c r="E103" s="68" t="inlineStr">
+        <is>
+          <t>腹满不食：中脘针，绝骨、下三里</t>
+        </is>
+      </c>
+      <c r="F103" s="68" t="inlineStr">
+        <is>
+          <t>구 포인터 "PDF 241–320쪽 L2972" 대체</t>
+        </is>
+      </c>
+      <c r="G103" s="68" t="inlineStr">
+        <is>
+          <t>1절</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="68" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴</t>
+        </is>
+      </c>
+      <c r="B104" s="68" t="inlineStr">
+        <is>
+          <t>03편 古代针灸方选解 按</t>
+        </is>
+      </c>
+      <c r="C104" s="68" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸证治通鉴/中国针灸证治通鉴_03_第壹编_第五至六篇_禁咒之法_古代针灸方选解.md</t>
+        </is>
+      </c>
+      <c r="D104" s="68" t="inlineStr">
+        <is>
+          <t>L260–262 (한글번역 L400–404)</t>
+        </is>
+      </c>
+      <c r="E104" s="68" t="inlineStr">
+        <is>
+          <t>"绝骨"穴不见于《明堂经》，后世医家或以之为悬钟穴，或以之为阳辅穴。敦煌卷子（编号：S.3347）…</t>
+        </is>
+      </c>
+      <c r="F104" s="68" t="inlineStr">
+        <is>
+          <t>구 포인터 "PDF 1–80쪽 L1236" 대체. 한글번역 L402는 "取光明及绝骨"의 광명·절골 누락</t>
+        </is>
+      </c>
+      <c r="G104" s="68" t="inlineStr">
+        <is>
+          <t>1절</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="68" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴</t>
+        </is>
+      </c>
+      <c r="B105" s="68" t="inlineStr">
+        <is>
+          <t>원문 20편 전체 집계</t>
+        </is>
+      </c>
+      <c r="C105" s="68" t="inlineStr">
+        <is>
+          <t>data/classics/中国针灸证治通鉴/*.md (한글번역 제외)</t>
+        </is>
+      </c>
+      <c r="D105" s="68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E105" s="68" t="inlineStr">
+        <is>
+          <t>悬钟·绝骨 출현 196회 / 165행</t>
+        </is>
+      </c>
+      <c r="F105" s="68" t="inlineStr">
+        <is>
+          <t>2026-10-25 재집계 일치</t>
+        </is>
+      </c>
+      <c r="G105" s="68" t="inlineStr">
+        <is>
+          <t>1절</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2776,267 +3278,321 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="65" t="inlineStr">
         <is>
-          <t>일시</t>
+          <t>papers.id</t>
         </is>
       </c>
       <c r="B1" s="65" t="inlineStr">
         <is>
-          <t>소스</t>
+          <t>연도</t>
         </is>
       </c>
       <c r="C1" s="65" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>저널</t>
         </is>
       </c>
       <c r="D1" s="65" t="inlineStr">
         <is>
-          <t>수집</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="E1" s="65" t="inlineStr">
         <is>
-          <t>중복제거</t>
+          <t>PMID</t>
         </is>
       </c>
       <c r="F1" s="65" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>DOI</t>
         </is>
       </c>
       <c r="G1" s="65" t="inlineStr">
         <is>
-          <t>쿼리</t>
+          <t>설계</t>
+        </is>
+      </c>
+      <c r="H1" s="65" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-04T09:51:54</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>pubmed</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A2" t="n">
+        <v>1624</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>针刺研究 46(1) (DB 표기: World Journal of Acupuncture-Moxibustion)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>关于悬钟穴定位的探讨 / Location of acupoint Xuanzhong (GB39) — 刘佳男 등</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.13702/j.1000-0607.200282 (본문 PDF)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>("GB39" OR "Xuanzhong" OR "懸鍾") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy)</t>
+          <t>문헌 연구(정위)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>T1 정위 근거(胫骨前嵴与腓骨前缘之间), 박동 촉지 곤란 지적</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-04T09:51:54</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>openalex</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>200</v>
-      </c>
-      <c r="D3" t="n">
-        <v>24</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A3" t="n">
+        <v>1610</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2003</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>대한침구학회지</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>치매와 관련된 뇌영역에 투사되는 경혈(SJ5·PC6·SP6·GB39)의 신경해부학적 연구</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>doi_starts_with:10.13703,title_and_abstract.search:"Xuanzhong" OR "GB39" | doi_starts_with:10.13702,title_and_abstract.search:"Xuanzhong" OR "GB39" | has_doi:tr…</t>
+          <t>동물 신경추적</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>T2 B-Check ④</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-04T09:51:54</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>crossref</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>200</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A4" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>대한한의학회지</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>양릉천-현종 전침치료가 뇌경색환자 및 정상인의 뇌혈류에 미치는 영향</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Xuanzhong acupuncture nerve reflex</t>
+          <t>인체 비RCT(배혈)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>T2 B-Check ④⑥</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-04T09:51:54</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1615</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2013</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>40</v>
-      </c>
-      <c r="E5" t="n">
-        <v>13</v>
-      </c>
-      <c r="F5" t="n">
-        <v>27</v>
+          <t>대한침구의학회지</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>懸鍾(GB39)·陽陵泉(GB34)의 電鍼 및 레이저침이 白鼠의 神經病理性 疼痛에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10.13045/acupunct.2013012</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>동물(배혈)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>T2 B-Check ③⑤</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-23T21:43:36</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>pubmed</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>200</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="A6" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Zhen Ci Yan Jiu</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Electroacupuncture at "Zusanli"(ST36) and "Xuanzhong"(GB39) improves inflammatory reactions…</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>31532135</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10.13702/j.1000-0607.180555</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>("GB39" OR "Xuanzhong" OR "悬钟") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy) | ("GB39" OR "Xuanzhong" OR "悬钟") AND ("Zhongguo Zhen Jiu"[Journal] OR "Zhen Ci Yan Jiu"[Journal])</t>
+          <t>동물(배혈)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>T2 B-Check ⑤</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-23T21:43:36</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>openalex</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>200</v>
-      </c>
-      <c r="D7" t="n">
-        <v>24</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="A7" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Zhongguo Zhen Jiu</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Electroacupuncture for the prevention of chemotherapy-induced peripheral neuropathy: an RCT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>39658376</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10.13703/j.0255-2930.20240222-k0001</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>doi_starts_with:10.13703,title_and_abstract.search:"Xuanzhong" OR "GB39" | doi_starts_with:10.13702,title_and_abstract.search:"Xuanzhong" OR "GB39" | has_doi:true,title_and_abstract.search:"Xuanzhong" OR "GB39" AND (acupuncture OR electroacupuncture)</t>
+          <t>인체 RCT(다혈위)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>T2 B-Check ⑥</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-23T21:43:36</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>crossref</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="A8" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Am J Physiol Regul Integr Comp Physiol</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Effect of electroacupuncture on pressor reflex during gastric distension</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>12388466</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10.1152/ajpregu.00192.2002</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Xuanzhong acupuncture nerve reflex</t>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>T1 B-Check ③~⑤ 유추</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-23T21:43:36</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>40</v>
-      </c>
-      <c r="E9" t="n">
-        <v>33</v>
-      </c>
-      <c r="F9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="A9" t="n">
+        <v>1620</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>针灸临床杂志</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>髓会绝骨的文献研究及临床应用概论</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>문헌 연구</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>참고(불산입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>불산입: 1842·1905·1845·1922(종설·데이터마이닝), 1910·1915·1924·1925·1911(GB39 포함/단독성 미확인), 1913(GB39 실측 아님)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3049,469 +3605,259 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="65" t="inlineStr">
         <is>
-          <t>위치</t>
+          <t>일시</t>
         </is>
       </c>
       <c r="B1" s="65" t="inlineStr">
         <is>
-          <t>원래 내용</t>
+          <t>소스</t>
         </is>
       </c>
       <c r="C1" s="65" t="inlineStr">
         <is>
-          <t>바꾼 내용</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="D1" s="65" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>수집</t>
+        </is>
+      </c>
+      <c r="E1" s="65" t="inlineStr">
+        <is>
+          <t>중복제거</t>
+        </is>
+      </c>
+      <c r="F1" s="65" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="G1" s="65" t="inlineStr">
+        <is>
+          <t>쿼리</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>머리말</t>
+          <t>2026-10-04T09:51:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>v2.6, 자침깊이 DB 링크가 로직 원칙 xlsx로 잘못 연결</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>v2.7 인용 블록(T1·T2 ARI 표기), 자침깊이 DB 링크 정정</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>final_GB39M.json notation; 02_Master_Datasets</t>
+          <t>pubmed</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>("GB39" OR "Xuanzhong" OR "懸鍾") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2.4·7.1·9절 《通考》 인용</t>
+          <t>2026-10-04T09:51:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>"懸鍾(絶骨)穴位於外踝上三寸, 腓骨前緣… 淺腓骨神經(L4-S1)… 腓骨動脈 관통지… '動脈'은 腓骨動脈 관통지의 박동"(통고 고증란), "5개 항목 완전 일치"</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>**가공 인용으로 삭제.** 실제 《通考》 원문(맥 기준 정위, 앞정강동맥, 경골 쪽, 名实分离, 名存实亡, 归经 불합리)으로 교체. 《通考》에 淺腓骨神經·腓骨動脈 관통가지 기술 없음</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>`针灸腧穴通考(下)_321-400.md` L431·437·542·548–552·615·658</t>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>doi_starts_with:10.13703,title_and_abstract.search:"Xuanzhong" OR "GB39" | doi_starts_with:10.13702,title_and_abstract.search:"Xuanzhong" OR "GB39" | has_doi:tr…</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1·2.2.1·5.1절 원문</t>
+          <t>2026-10-04T09:51:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>《甲乙》 "在足外踝上三寸動脈中", 《明堂》 "在足外踝上三寸"</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>"在足外踝上三寸動者脈中, 足三陽絡, 按之陽明脈絶乃取之" 전문 복원</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>`中国针灸穴位通鉴(下卷)_161-240.md` L54; 《通考》 L421</t>
+          <t>crossref</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Xuanzhong acupuncture nerve reflex</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2.2.1절 銅人·千金·大成</t>
+          <t>2026-10-04T09:51:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>《銅人》 "絶骨穴在足外踝上三寸", 《千金》 "絶骨, 在外踝上三寸", 《大成》 "足外踝上三寸, 足少陽, 陽維之會"</t>
+          <t>all</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>《銅人》 5:20 "在足外踝上三寸動脈中", 《千金》 卷29 "悬钟，一名绝骨，在外踝上三寸动者中，足三阳络", 《大成》 7:209 "足外踝上三寸動脈中，尋摸尖骨者是。足三陽之大絡，按之陽明脈絶乃取之"</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>《通鉴》 L90·110; 《通考》 L426</t>
-        </is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2.1절 이명</t>
+          <t>2026-10-23T21:43:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>絶骨 "甲乙經 이후 모든 문헌에서 동일혈, 혼용 위험 없음", "비골의 고대 이칭", 縣鍾</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>絶骨은 《明堂》에 없고 《千金》 卷29에서 처음 현종 이명. KJH·2대 교재가 GB38에도 등재 → 혼용 위험 높음. 縣鍾 삭제, 足三陽絡 추가</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>KJH 경혈 종합 목록 344·345행; 공통교재·김재효 xlsx 342·343행; 《通鉴》 L342; 《通考》 L431</t>
+          <t>pubmed</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>("GB39" OR "Xuanzhong" OR "悬钟") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy) | ("GB39" OR "Xuanzhong" OR "悬钟") AND ("Zhongguo Zhen Jiu"[Journal] OR "Zhen Ci Yan Jiu"[Journal])</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2.2.2·2.2.3절 깊이</t>
+          <t>2026-10-23T21:43:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>"갑을경 34"를 깊이 값처럼 수록, μ 6.2푼·σ 1.0푼</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>34는 배열 번호로 명시, 통계 삭제, 《脉经》·《玉龙经》·《指微》·窦氏·横透 등 이질 심도 추가</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>자침깊이 xlsx 시트1 344행; 《通鉴》 L234–274</t>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>doi_starts_with:10.13703,title_and_abstract.search:"Xuanzhong" OR "GB39" | doi_starts_with:10.13702,title_and_abstract.search:"Xuanzhong" OR "GB39" | has_doi:true,title_and_abstract.search:"Xuanzhong" OR "GB39" AND (acupuncture OR electroacupuncture)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2.3·3.2절 주치</t>
+          <t>2026-10-23T21:43:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$P_{single}$ = 頸項强痛·落枕·下肢痿痹·足脛疼痛, 원주치 누락</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>$P_{single}$ = 腹满·胃中有热·不嗜食·小儿腹满(《明堂》). 頸項强 = 《千金》 卷18 絶骨 주치 혼입, 落枕 = 현대 《针灸学简编》(배오), 五淋·湿痹 = 陽輔 주치 혼입</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>《通考》 L542·627–647·686; 《通鉴》 L154–156·230·342</t>
+          <t>crossref</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Xuanzhong acupuncture nerve reflex</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4.2절 Δ</t>
+          <t>2026-10-23T21:43:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.3~0.7cm, "분리 기준 미달, 단일 분석"</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Δ ≈ 20~35mm(채점자 2인 독립 추정) → T1·T2 분기, 7절 신설</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>final_GB39M.json override_note; papers.id 1624</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>5.1·6.2절 "動脈中" 실체</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>종아리동맥 관통가지</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>앞정강동맥(종아리동맥 관통가지 해석은 원전 근거 없음)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>《通考》 L548–552; 《通鉴》 L74; papers.id 1624</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>5.3·8.1절 Layer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>얕은종아리신경 8~14mm(Layer 3b), 비골 골막 Layer 4, 피질골 "金禁"</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>얕은종아리신경 = Layer 1(피하), Layer 4 = 앞정강동·정맥 + 깊은종아리신경, Layer 5 = 골막. "金禁" 삭제(DB에 '0' 없음)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>정본 Rank 5 Layer 정의; 자침깊이 xlsx 344행; B1-01·B1-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>5.2절 안전</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>"비골동맥 본간 손상 위험 없음", Layer 4 위험 구조 누락</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>T1·T2별 Layer 4(앞정강동맥·깊은종아리신경) 접촉 가능성과 심자 기록(《指微》 46mm, 窦氏 57.5mm) 명시</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>final_GB39M.json S_safety 근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>6.1·9절 기전</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>"L4-S1 → C3-C5 분절 상행 → 경항부 근이완 반사", "골막 자극 = 髓會 기반"</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>삭제. B-Check 근거 기반 가설도로 교체</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>등록부·Layer A 근거 없음(final T2 override_note)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Rank 5 교재표</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>"상호 보완적 정합", "완벽 대조"</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>실제 차이(긴엄지굽힘근·종아리동정맥·셋째종아리근 vs 긴종아리근) 분석</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>공통교재·김재효 xlsx 각 343행</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>8절</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Layer A·B-Check·검색 로그 없음</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>papers.id 표(1624 정위 결론 인용 포함), T1·T2 B-Check(5/12·6/12), sync_log 표 추가</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>pack_GB39.md; final_GB39M.json bcheck; 1624 본문 PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>8절 papers.id 1624 서지</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>(인용 없음)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>针刺研究 2021;46(1), DOI 10.13702/j.1000-0607.200282. 마스터 DB의 저널 표기(World Journal of Acupuncture-Moxibustion)는 본문 PDF와 다름(DB 정정 필요)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>`03_주제별_경혈고증_연구보고서/현종혈_고증_및_문헌연구/04_참고논문_PDF/2021-침자연구-Location of acupoint Xuanzhong_GB39.pdf`</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>8절 감사표</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>보고서↔엑셀 "전 항목 일치" 정합성 감사</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>삭제(동일 산출물 간 대조는 신뢰도 근거가 아님, 정본 Rank 7)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>정본 Rank 7 상호 검증 조항</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>10절</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>v2.6 5요인 ARI</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>T1 51.2 ± 0 (D·H) / T2 55 ± 0 (C, 가중치 민감), 하위 항목·게이트·분기·조정 기록</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>final_GB39M.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>10절</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>구판 v2.6 점수 93.6(비교 불가)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>구판 보고서 `_구판_v2.6/`</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>확인 못 한 항목</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>《難經》 45難 "髓會絶骨"의 陽輔 귀속설은 3대 원전 청크에서 원문을 직접 찾지 못해 "귀속 미확정"으로만 기술. 《通考》 "人体测量学调查"의 서지 미확인. T1·T2의 mm 단위 Δ·깊이는 채점자 추정이며 영상 실측 없음</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가. T1 ARI-Core 51.2 ± 0 (D·H)·T2 55.0 ± 0 (C) 불변</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>fma_query.py profile GB39; 보고서 4·6·8절·부록 A</t>
-        </is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>40</v>
+      </c>
+      <c r="E9" t="n">
+        <v>33</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3520,6 +3866,504 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="65" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+      <c r="B1" s="65" t="inlineStr">
+        <is>
+          <t>원래 내용</t>
+        </is>
+      </c>
+      <c r="C1" s="65" t="inlineStr">
+        <is>
+          <t>바꾼 내용</t>
+        </is>
+      </c>
+      <c r="D1" s="65" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>머리말</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>v2.6, 자침깊이 DB 링크가 로직 원칙 xlsx로 잘못 연결</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>v2.7 인용 블록(T1·T2 ARI 표기), 자침깊이 DB 링크 정정</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>final_GB39M.json notation; 02_Master_Datasets</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2.4·7.1·9절 《通考》 인용</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>"懸鍾(絶骨)穴位於外踝上三寸, 腓骨前緣… 淺腓骨神經(L4-S1)… 腓骨動脈 관통지… '動脈'은 腓骨動脈 관통지의 박동"(통고 고증란), "5개 항목 완전 일치"</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>**가공 인용으로 삭제.** 실제 《通考》 원문(맥 기준 정위, 앞정강동맥, 경골 쪽, 名实分离, 名存实亡, 归经 불합리)으로 교체. 《通考》에 淺腓骨神經·腓骨動脈 관통가지 기술 없음</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>`针灸腧穴通考(下)_321-400.md` L431·437·542·548–552·615·658</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1·2.2.1·5.1절 원문</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>《甲乙》 "在足外踝上三寸動脈中", 《明堂》 "在足外踝上三寸"</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>"在足外踝上三寸動者脈中, 足三陽絡, 按之陽明脈絶乃取之" 전문 복원</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>`中国针灸穴位通鉴(下卷)_161-240.md` L54; 《通考》 L421</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2.2.1절 銅人·千金·大成</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>《銅人》 "絶骨穴在足外踝上三寸", 《千金》 "絶骨, 在外踝上三寸", 《大成》 "足外踝上三寸, 足少陽, 陽維之會"</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>《銅人》 5:20 "在足外踝上三寸動脈中", 《千金》 卷29 "悬钟，一名绝骨，在外踝上三寸动者中，足三阳络", 《大成》 7:209 "足外踝上三寸動脈中，尋摸尖骨者是。足三陽之大絡，按之陽明脈絶乃取之"</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>《通鉴》 L90·110; 《通考》 L426</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2.1절 이명</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>絶骨 "甲乙經 이후 모든 문헌에서 동일혈, 혼용 위험 없음", "비골의 고대 이칭", 縣鍾</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>絶骨은 《明堂》에 없고 《千金》 卷29에서 처음 현종 이명. KJH·2대 교재가 GB38에도 등재 → 혼용 위험 높음. 縣鍾 삭제, 足三陽絡 추가</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>KJH 경혈 종합 목록 344·345행; 공통교재·김재효 xlsx 342·343행; 《通鉴》 L342; 《通考》 L431</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2.2.2·2.2.3절 깊이</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>"갑을경 34"를 깊이 값처럼 수록, μ 6.2푼·σ 1.0푼</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>34는 배열 번호로 명시, 통계 삭제, 《脉经》·《玉龙经》·《指微》·窦氏·横透 등 이질 심도 추가</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>자침깊이 xlsx 시트1 344행; 《通鉴》 L234–274</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2.3·3.2절 주치</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>$P_{single}$ = 頸項强痛·落枕·下肢痿痹·足脛疼痛, 원주치 누락</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>$P_{single}$ = 腹满·胃中有热·不嗜食·小儿腹满(《明堂》). 頸項强 = 《千金》 卷18 絶骨 주치 혼입, 落枕 = 현대 《针灸学简编》(배오), 五淋·湿痹 = 陽輔 주치 혼입</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>《通考》 L542·627–647·686; 《通鉴》 L154–156·230·342</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4.2절 Δ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.3~0.7cm, "분리 기준 미달, 단일 분석"</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Δ ≈ 20~35mm(채점자 2인 독립 추정) → T1·T2 분기, 7절 신설</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>final_GB39M.json override_note; papers.id 1624</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5.1·6.2절 "動脈中" 실체</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>종아리동맥 관통가지</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>앞정강동맥(종아리동맥 관통가지 해석은 원전 근거 없음)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>《通考》 L548–552; 《通鉴》 L74; papers.id 1624</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5.3·8.1절 Layer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>얕은종아리신경 8~14mm(Layer 3b), 비골 골막 Layer 4, 피질골 "金禁"</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>얕은종아리신경 = Layer 1(피하), Layer 4 = 앞정강동·정맥 + 깊은종아리신경, Layer 5 = 골막. "金禁" 삭제(DB에 '0' 없음)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>정본 Rank 5 Layer 정의; 자침깊이 xlsx 344행; B1-01·B1-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5.2절 안전</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>"비골동맥 본간 손상 위험 없음", Layer 4 위험 구조 누락</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>T1·T2별 Layer 4(앞정강동맥·깊은종아리신경) 접촉 가능성과 심자 기록(《指微》 46mm, 窦氏 57.5mm) 명시</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>final_GB39M.json S_safety 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6.1·9절 기전</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>"L4-S1 → C3-C5 분절 상행 → 경항부 근이완 반사", "골막 자극 = 髓會 기반"</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>삭제. B-Check 근거 기반 가설도로 교체</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>등록부·Layer A 근거 없음(final T2 override_note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Rank 5 교재표</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>"상호 보완적 정합", "완벽 대조"</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>실제 차이(긴엄지굽힘근·종아리동정맥·셋째종아리근 vs 긴종아리근) 분석</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>공통교재·김재효 xlsx 각 343행</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>8절</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Layer A·B-Check·검색 로그 없음</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>papers.id 표(1624 정위 결론 인용 포함), T1·T2 B-Check(5/12·6/12), sync_log 표 추가</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>pack_GB39.md; final_GB39M.json bcheck; 1624 본문 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>8절 papers.id 1624 서지</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>(인용 없음)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>针刺研究 2021;46(1), DOI 10.13702/j.1000-0607.200282. 마스터 DB의 저널 표기(World Journal of Acupuncture-Moxibustion)는 본문 PDF와 다름(DB 정정 필요)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>`03_주제별_경혈고증_연구보고서/현종혈_고증_및_문헌연구/04_참고논문_PDF/2021-침자연구-Location of acupoint Xuanzhong_GB39.pdf`</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>8절 감사표</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>보고서↔엑셀 "전 항목 일치" 정합성 감사</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>삭제(동일 산출물 간 대조는 신뢰도 근거가 아님, 정본 Rank 7)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>정본 Rank 7 상호 검증 조항</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>10절</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>v2.6 5요인 ARI</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>T1 51.2 ± 0 (D·H) / T2 55 ± 0 (C, 가중치 민감), 하위 항목·게이트·분기·조정 기록</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>final_GB39M.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>10절</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>구판 v2.6 점수 93.6(비교 불가)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>구판 보고서 `_구판_v2.6/`</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>확인 못 한 항목</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>《難經》 45難 "髓會絶骨"의 陽輔 귀속설은 3대 원전 청크에서 원문을 직접 찾지 못해 "귀속 미확정"으로만 기술. 《通考》 "人体测量学调查"의 서지 미확인. T1·T2의 mm 단위 Δ·깊이는 채점자 추정이며 영상 실측 없음</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가. T1 ARI-Core 51.2 ± 0 (D·H)·T2 55.0 ± 0 (C) 불변</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>fma_query.py profile GB39; 보고서 4·6·8절·부록 A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="70" t="inlineStr">
+        <is>
+          <t>Framework 2.7.7 (2026-10-25)</t>
+        </is>
+      </c>
+      <c r="B22" s="70" t="inlineStr">
+        <is>
+          <t>3대 원전; Dual-Target T1(고전)/T2(WHO), 분기 기준 Δ&gt;15mm; S_orig④ 通考 교감; 证治通鉴 PDF 기준 포인터</t>
+        </is>
+      </c>
+      <c r="C22" s="70" t="inlineStr">
+        <is>
+          <t>4대 원전(经络通鉴 01·04·05·11·28·34·35·36편 — Sheet1 하단 블록); Tri-Target: 구 T1 → Target 1≡2, 구 T2 → Target 3, 쌍별 Δ(T1–T2 ≤10mm 병합, T1/T2–T3 약 20~35mm 분기, 기준 Δ&gt;10mm) — 분기추론_TriTarget 시트; ④ 通考·经络通鉴 교감 재점검 불변; ARI·SI 점수 불변; B-Check Target 표지 T1≡2/T3; 证治通鉴 포인터를 편·행+한글번역으로 갱신</t>
+        </is>
+      </c>
+      <c r="D22" s="70" t="inlineStr">
+        <is>
+          <t>프레임워크 2.7.7–2.7.8; data/classics/中国针灸经络通鉴/ 각 편; data/classics/中国针灸证治通鉴/ 03·09·17·19편(+한글번역)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5940,10 +6784,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11757,7 +12601,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T1 고전 맥동점(外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
+          <t>Target 1≡2 고전 맥동점(구 T1; 外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11788,7 +12632,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T1 고전 맥동점(外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
+          <t>Target 1≡2 고전 맥동점(구 T1; 外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -11821,7 +12665,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T1 고전 맥동점(外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
+          <t>Target 1≡2 고전 맥동점(구 T1; 外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -11852,7 +12696,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T1 고전 맥동점(外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
+          <t>Target 1≡2 고전 맥동점(구 T1; 外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -11883,7 +12727,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T1 고전 맥동점(外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
+          <t>Target 1≡2 고전 맥동점(구 T1; 外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -11904,7 +12748,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T1 고전 맥동점(外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
+          <t>Target 1≡2 고전 맥동점(구 T1; 外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -11925,7 +12769,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T1 고전 맥동점(外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
+          <t>Target 1≡2 고전 맥동점(구 T1; 外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -11946,12 +12790,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T1 고전 맥동점(外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
+          <t>Target 1≡2 고전 맥동점(구 T1; 外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S_orig 하위 ④ 通考 교감</t>
+          <t>S_orig 하위 ④ 通考·经络通鉴 교감</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -11963,11 +12807,16 @@
       <c r="E9" t="n">
         <v>75</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-25 经络通鉴 재점검(01편 L1035·L2017, 04편 L1016, 36편 L193·209): 새 실측 서지·이문 교정 없음 → 단계 이동 없음, 불변</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T2 WHO 비골 전연(外踝尖上3寸, 腓骨前緣)</t>
+          <t>Target 3 WHO 비골 전연(구 T2; 外踝尖上3寸, 腓骨前緣)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11998,7 +12847,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T2 WHO 비골 전연(外踝尖上3寸, 腓骨前緣)</t>
+          <t>Target 3 WHO 비골 전연(구 T2; 外踝尖上3寸, 腓骨前緣)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -12029,7 +12878,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T2 WHO 비골 전연(外踝尖上3寸, 腓骨前緣)</t>
+          <t>Target 3 WHO 비골 전연(구 T2; 外踝尖上3寸, 腓骨前緣)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -12060,7 +12909,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T2 WHO 비골 전연(外踝尖上3寸, 腓骨前緣)</t>
+          <t>Target 3 WHO 비골 전연(구 T2; 外踝尖上3寸, 腓骨前緣)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -12091,7 +12940,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T2 WHO 비골 전연(外踝尖上3寸, 腓骨前緣)</t>
+          <t>Target 3 WHO 비골 전연(구 T2; 外踝尖上3寸, 腓骨前緣)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -12112,7 +12961,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T2 WHO 비골 전연(外踝尖上3寸, 腓骨前緣)</t>
+          <t>Target 3 WHO 비골 전연(구 T2; 外踝尖上3寸, 腓骨前緣)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -12133,7 +12982,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T2 WHO 비골 전연(外踝尖上3寸, 腓骨前緣)</t>
+          <t>Target 3 WHO 비골 전연(구 T2; 外踝尖上3寸, 腓骨前緣)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -12154,12 +13003,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T2 WHO 비골 전연(外踝尖上3寸, 腓骨前緣)</t>
+          <t>Target 3 WHO 비골 전연(구 T2; 外踝尖上3寸, 腓骨前緣)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S_orig 하위 ④ 通考 교감</t>
+          <t>S_orig 하위 ④ 通考·经络通鉴 교감</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -12171,7 +13020,13 @@
       <c r="E17" t="n">
         <v>75</v>
       </c>
-    </row>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-25 经络通鉴 재점검(01편 L1035·L2017, 04편 L1016, 36편 L193·209): 새 실측 서지·이문 교정 없음 → 단계 이동 없음, 불변</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="65" t="inlineStr">
         <is>
@@ -12222,7 +13077,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T1 고전 맥동점(外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
+          <t>Target 1≡2 고전 맥동점(구 T1; 外踝上三寸 動者脈中, 按之陽明脈絶 = 앞정강동맥)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -12263,7 +13118,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T2 WHO 비골 전연(外踝尖上3寸, 腓骨前緣)</t>
+          <t>Target 3 WHO 비골 전연(구 T2; 外踝尖上3寸, 腓骨前緣)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -12301,6 +13156,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -12309,7 +13165,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Δ_discrepancy ≈ 20~35mm (&gt;15mm, 채점자 2인 독립 추정) → 분기</t>
+          <t>Tri-Target: Target 1≡2 vs Target 3, Δ_discrepancy ≈ 20~35mm (&gt; 10mm, 채점자 2인 독립 추정; Target 1–2 ≤ 10mm 병합) — 분기추론_TriTarget 시트</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -12385,553 +13241,346 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="65" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="B1" s="65" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="C1" s="65" t="inlineStr">
-        <is>
-          <t>채점자 A</t>
-        </is>
-      </c>
-      <c r="D1" s="65" t="inlineStr">
-        <is>
-          <t>채점자 B</t>
-        </is>
-      </c>
-      <c r="E1" s="65" t="inlineStr">
-        <is>
-          <t>최종</t>
-        </is>
-      </c>
-      <c r="F1" s="65" t="inlineStr">
-        <is>
-          <t>Layer B 참조 ID</t>
-        </is>
-      </c>
-      <c r="G1" s="65" t="inlineStr">
-        <is>
-          <t>papers.id</t>
-        </is>
-      </c>
-      <c r="H1" s="65" t="inlineStr">
-        <is>
-          <t>근거(A)</t>
-        </is>
-      </c>
-      <c r="I1" s="65" t="inlineStr">
-        <is>
-          <t>근거(B)</t>
+      <c r="B1" s="69" t="inlineStr">
+        <is>
+          <t>정의</t>
+        </is>
+      </c>
+      <c r="C1" s="69" t="inlineStr">
+        <is>
+          <t>원전 근거</t>
+        </is>
+      </c>
+      <c r="D1" s="69" t="inlineStr">
+        <is>
+          <t>X·Y 위치(체표)</t>
+        </is>
+      </c>
+      <c r="E1" s="69" t="inlineStr">
+        <is>
+          <t>Z(깊이, 추정)</t>
+        </is>
+      </c>
+      <c r="F1" s="69" t="inlineStr">
+        <is>
+          <t>자입 기준점</t>
+        </is>
+      </c>
+      <c r="G1" s="69" t="inlineStr">
+        <is>
+          <t>구판 표기 대응</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>B1-01, B1-03, B1-06, B2-09</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1624</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>전경골동·정맥 + 깊은종아리신경은 규범 해부서와 2대 교재(전경골동맥 등재)로 확인되나 T1 위치 특이 실측(B2 영상·사체)이 없어 1.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>T1 실체 = 전경골동맥+심비골신경(L4-L5)이라는 해석은 규범 해부와 통감·통고 해석으로 지지되나 혈위 특이 심도 실측 없음, 1624는 박동 촉지 곤란을 지적 → 1</t>
+      <c r="A2" s="70" t="inlineStr">
+        <is>
+          <t>Target 1 (고전 문헌 위치)</t>
+        </is>
+      </c>
+      <c r="B2" s="70" t="inlineStr">
+        <is>
+          <t>최초 기술 문구 위치</t>
+        </is>
+      </c>
+      <c r="C2" s="70" t="inlineStr">
+        <is>
+          <t>《明堂》 在足外踝上三寸動者(脈)中，足三陽絡，按之陽明脈絶乃取之 (通考(下)_321-400 L421; 穴位通鉴(下卷)_161-240 L54)</t>
+        </is>
+      </c>
+      <c r="D2" s="70" t="inlineStr">
+        <is>
+          <t>Y 外踝上3寸; X는 맥동으로만 지정 → Target 2와 같은 점</t>
+        </is>
+      </c>
+      <c r="E2" s="70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" s="70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="70" t="inlineStr">
+        <is>
+          <t>Target 1≡2로 병합</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>B1-03, B3-05</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>깊은종아리신경 L4~L5(S1) 근절·피절 vs 《明堂》 원주치 표적(위, T6~T9 내장절) 분절 불일치. 하지 자극의 위운동 조절은 상척수성(미주) 체성-자율 반사로 설명되는 유추 수준 → 1.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>심비골신경 L4-L5(피절 L5) vs 원 주치 위장(腹满·胃中有热·不嗜食, 내장절 T6-T9/미주) 분절 불일치; 하지-위 반사는 상척수(미주) 경로로만 연결되는 유추 → 1</t>
+      <c r="A3" s="70" t="inlineStr">
+        <is>
+          <t>Target 2 (촉진 실체화 위치)</t>
+        </is>
+      </c>
+      <c r="B3" s="70" t="inlineStr">
+        <is>
+          <t>動者脈中·按之陽明脈絶의 해부 실체</t>
+        </is>
+      </c>
+      <c r="C3" s="70" t="inlineStr">
+        <is>
+          <t>通考 L548–552; 经络通鉴 01편 L2017; 穴位通鉴 L74; papers.id 1624</t>
+        </is>
+      </c>
+      <c r="D3" s="70" t="inlineStr">
+        <is>
+          <t>경골 앞모서리–종아리뼈 앞모서리 사이 경골 쪽 앞정강동맥(FMA:43894) 박동선</t>
+        </is>
+      </c>
+      <c r="E3" s="70" t="inlineStr">
+        <is>
+          <t>약 10~20mm(L4 신경혈관속, 채점자 추정)</t>
+        </is>
+      </c>
+      <c r="F3" s="70" t="inlineStr">
+        <is>
+          <t>간극 표현 없음 → 형식상 미표시(해부상 앞정강근 힘줄–긴엄지폄근 FMA:22533 사이, B1-01 추론)</t>
+        </is>
+      </c>
+      <c r="G3" s="70" t="inlineStr">
+        <is>
+          <t>Target 1≡2로 병합</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>B3-05, B3-06, B3-12</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>깊은종아리신경 심부 근육 구심(group III/IV, Aδ/C) 관여는 ST36-37 등 타 경혈·마취 동물에서 검증된 범위 밖 유추 → 1.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>심부 근·혈관주위 Ⅲ/Ⅳ군·Aβ/Aδ 구심섬유는 마취 동물 일반 기전, T1 미검증 범위 밖 → 1</t>
+      <c r="A4" s="70" t="inlineStr">
+        <is>
+          <t>Target 1≡2 (병합)</t>
+        </is>
+      </c>
+      <c r="B4" s="70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" s="70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="70" t="inlineStr">
+        <is>
+          <t>위 Target 2 좌표</t>
+        </is>
+      </c>
+      <c r="E4" s="70" t="inlineStr">
+        <is>
+          <t>위와 같음</t>
+        </is>
+      </c>
+      <c r="F4" s="70" t="inlineStr">
+        <is>
+          <t>위와 같음</t>
+        </is>
+      </c>
+      <c r="G4" s="70" t="inlineStr">
+        <is>
+          <t>구 T1 "고전 맥동점" → Target 1≡2 (점수 승계: A·B 이중 채점)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>B3-05, B3-12</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>후지 체성자극 → 연수(rVLM/NTS·미주 운동핵) 경로는 마취 쥐·고양이, 타 경혈 근거 → 1.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>후지 자극→상척수 미주/rVLM 경로는 동물·타 부위(비골신경 전침) 근거 유추</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>B3-05</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>원주치 '腹满·胃中有热·不嗜食'과 하지 자극의 미주성 위운동 촉진 방향은 마취 쥐 일반 기전으로 유추 가능하나 T1 특이 근거 없음 → 1.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>마취 쥐 후지 체성 자극의 위운동 미주성 촉진 반사가 원 주치(위 병증) 방향과 개념상 부합하나 T1 직접 근거 없음; 1904는 위팽만 심혈관반사 지표로 위 기능 효과 아님</t>
+      <c r="A5" s="70" t="inlineStr">
+        <is>
+          <t>Target 3 (WHO 표준 위치)</t>
+        </is>
+      </c>
+      <c r="B5" s="70" t="inlineStr">
+        <is>
+          <t>현대 표준 정위</t>
+        </is>
+      </c>
+      <c r="C5" s="70" t="inlineStr">
+        <is>
+          <t>WHO 2008; 6·7판 교재 外踝尖上3寸，腓骨前缘 (通考 L569)</t>
+        </is>
+      </c>
+      <c r="D5" s="70" t="inlineStr">
+        <is>
+          <t>종아리뼈 앞모서리</t>
+        </is>
+      </c>
+      <c r="E5" s="70" t="inlineStr">
+        <is>
+          <t>표준 직자 5~8푼 = 11.5~18.4mm</t>
+        </is>
+      </c>
+      <c r="F5" s="70" t="inlineStr">
+        <is>
+          <t>종아리뼈 앞모서리(緣): 긴발가락폄근 FMA:22534(앞칸 FMA:85203)–짧은종아리근 FMA:22540(가쪽칸 FMA:85206) 근간 경계</t>
+        </is>
+      </c>
+      <c r="G5" s="70" t="inlineStr">
+        <is>
+          <t>구 T2 "WHO 비골 전연" → Target 3 (점수 승계)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>B4-05</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>T1 위치 자침의 인체 신경영상·자율신경 지표·임상 연구 없음. 혈위 특이성 논쟁(B4-05) 미해결 → 0.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>T1 정위로 자침한 인체 생리·임상 연구 없음</t>
-        </is>
-      </c>
+      <c r="A7" s="69" t="inlineStr">
+        <is>
+          <t>쌍</t>
+        </is>
+      </c>
+      <c r="B7" s="69" t="inlineStr">
+        <is>
+          <t>Δ (추정)</t>
+        </is>
+      </c>
+      <c r="C7" s="69" t="inlineStr">
+        <is>
+          <t>추정 근거</t>
+        </is>
+      </c>
+      <c r="D7" s="69" t="inlineStr">
+        <is>
+          <t>판정 (Δ &gt; 10mm 분기)</t>
+        </is>
+      </c>
+      <c r="E7" s="69" t="inlineStr">
+        <is>
+          <t>15mm→10mm 기준 변경 영향</t>
+        </is>
+      </c>
+      <c r="F7" s="69" t="inlineStr"/>
+      <c r="G7" s="69" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>미부합 → 반사 기전 가설</t>
+      <c r="A8" s="70" t="inlineStr">
+        <is>
+          <t>Target 1–Target 2</t>
+        </is>
+      </c>
+      <c r="B8" s="70" t="inlineStr">
+        <is>
+          <t>≤ 10mm (사실상 0, 추정)</t>
+        </is>
+      </c>
+      <c r="C8" s="70" t="inlineStr">
+        <is>
+          <t>Target 1 횡위치가 맥동으로만 정해짐 → 정의상 같은 점</t>
+        </is>
+      </c>
+      <c r="D8" s="70" t="inlineStr">
+        <is>
+          <t>병합</t>
+        </is>
+      </c>
+      <c r="E8" s="70" t="inlineStr">
+        <is>
+          <t>변화 없음</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>B1-01, B1-03, B2-09</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>얕은·깊은종아리신경, 앞정강동정맥, 폄근군은 규범 해부·2대 교재로 확인되나 GB39 특이 영상·사체 실측 논문 없음(B2 2점 조건 미충족). 보고서의 '비골동맥 관통지=動脈中' 주장은 《通考》의 앞정강동맥 해석과 불일치.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>교재 2종이 얕은·깊은종아리신경과 앞정강동맥을 지정하지만 혈관 구성이 서로 다르고 혈위 특이 영상 실측(B2-10 유형)이 없음. 보고서의 '비골동맥 관통지=動脈' 동정은 通考와 상충함.</t>
+      <c r="A9" s="70" t="inlineStr">
+        <is>
+          <t>Target 1–Target 3</t>
+        </is>
+      </c>
+      <c r="B9" s="70" t="inlineStr">
+        <is>
+          <t>약 20~35mm (추정)</t>
+        </is>
+      </c>
+      <c r="C9" s="70" t="inlineStr">
+        <is>
+          <t>채점자 B X축 20~30mm(중앙값 약 25mm), 채점자 A 3D 20~35mm; 영상 실측 없음</t>
+        </is>
+      </c>
+      <c r="D9" s="70" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="E9" s="70" t="inlineStr">
+        <is>
+          <t>변화 없음(15mm도 초과)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>B1-03, B3-05, B3-20</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>L4~S1 피절·근절은 국소 주치(下肢痿痺·足脛痛)와 정합. 보고서의 'L4-S1→C3-C5 체성-체성 이완 반사'(頸項强痛)는 분절 근거 없음. 명당경 원주치(위병, T6~T9)와도 분절 불일치.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>L4~S1 피절·근절은 국소 하지 주치(下肢痿痺·足脛痛)와 맞음. 원전 단독 주치인 腹滿·胃中有熱·不嗜食(위 T6~T9)과 보고서가 주장한 頸項强痛(C3~C5)은 분절이 불일치하여 상척수성 유추만 가능함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>B3-04, B3-06, B3-11, B3-17</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1615</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>침 자극 구심 섬유(Aδ/C) 일반 틀과 GB39·GB34 전침 진통 동물 연구(복합 혈위)만 존재 — 유추·동물 한정.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>구심 섬유형에 관한 일반 기전과 하지 심부 근막 PROKR2 기전(ST36 검증)은 범위 밖이므로 유추로만 인정함. GB39 고유의 섬유형 연구는 없음.</t>
+      <c r="A10" s="70" t="inlineStr">
+        <is>
+          <t>Target 2–Target 3</t>
+        </is>
+      </c>
+      <c r="B10" s="70" t="inlineStr">
+        <is>
+          <t>약 20~35mm (추정)</t>
+        </is>
+      </c>
+      <c r="C10" s="70" t="inlineStr">
+        <is>
+          <t>Target 1–3과 같음</t>
+        </is>
+      </c>
+      <c r="D10" s="70" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="E10" s="70" t="inlineStr">
+        <is>
+          <t>변화 없음</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>B3-05, B3-07, B3-11</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1610, 1612</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>GB39 관련 뇌영역 투사 추적(동물), GB34-GB39 전침 뇌혈류 변화(인체, 복합 혈위)로 중추 관여는 간접 시사. 경로 특정 근거 없음.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>GB39 신경추적 연구(1610, 동물)와 진통 중추 경로에 관한 일반 기전뿐임. 보고서의 'C3-C5 분절 상행 반사'는 근거가 없음.</t>
+          <t>Rank 7 판정</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>독립 Target 2개(Target 1≡2, Target 3). ΔARI-Core = 55.0 − 51.2 = 3.8 &lt; 10 → 우위 없음, 병기. 단일 채점(예비) Target 없음.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>B3-05, B3-11, B3-16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>1615, 1903</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>국소 진통·항염 방향은 하지 통증 주치와 동물 수준에서 부합. 頸項强痛 원격 효과·髓會(골수) 효과의 원심 경로 근거 없음.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>사지 자극이 위 운동과 염증을 조절한다는 기전은 마취 쥐·마우스 ST36에서 나온 유추이고, ST36+GB39 병용 동물 연구(1903)가 있음. 고전 주치(위열·복만)의 효과 방향과 직접 대응하는 GB39 연구는 없음.</t>
+          <t>제외한 촉진 표현</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>尋摸尖骨者是(《大成》), 绝骨尖间筋骨缝中(《循经考穴编》), 掐时与跷脉相应处(돈황 사본), 寻小骨头绝陷中(《三家脚气论》) — 絶骨 계통 골성 촉진, 원천 아님 → Target 2 미사용(Target 3 계통, 추정)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>6</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>B4-03, B4-04, B4-05</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1612, 1902</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>인체 근거는 복합 혈위 전침(뇌혈류 비RCT, CIPN RCT)뿐으로 GB39 특이 전환 근거 아님. B4-04·B4-05의 혈위 비특이성 반증 병기 필요.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>GB34-GB39 전침 인체 뇌혈류 연구(비RCT, 배혈)가 1편 있음. 혈위 특이성 반증(B4-04·B4-05)을 함께 고려해 1점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>미부합 → 반사 기전 가설</t>
+          <t>구판 시트 주의</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sheet3_노이즈여과_3D좌표의 Step 3(Δ≈0.3–0.5cm)은 구판 v2.6 값으로 폐기됨 — 본 시트가 현행</t>
         </is>
       </c>
     </row>
@@ -12946,319 +13595,553 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="65" t="inlineStr">
         <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="65" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C1" s="65" t="inlineStr">
+        <is>
+          <t>채점자 A</t>
+        </is>
+      </c>
+      <c r="D1" s="65" t="inlineStr">
+        <is>
+          <t>채점자 B</t>
+        </is>
+      </c>
+      <c r="E1" s="65" t="inlineStr">
+        <is>
+          <t>최종</t>
+        </is>
+      </c>
+      <c r="F1" s="65" t="inlineStr">
+        <is>
+          <t>Layer B 참조 ID</t>
+        </is>
+      </c>
+      <c r="G1" s="65" t="inlineStr">
+        <is>
           <t>papers.id</t>
         </is>
       </c>
-      <c r="B1" s="65" t="inlineStr">
-        <is>
-          <t>연도</t>
-        </is>
-      </c>
-      <c r="C1" s="65" t="inlineStr">
-        <is>
-          <t>저널</t>
-        </is>
-      </c>
-      <c r="D1" s="65" t="inlineStr">
-        <is>
-          <t>제목</t>
-        </is>
-      </c>
-      <c r="E1" s="65" t="inlineStr">
-        <is>
-          <t>PMID</t>
-        </is>
-      </c>
-      <c r="F1" s="65" t="inlineStr">
-        <is>
-          <t>DOI</t>
-        </is>
-      </c>
-      <c r="G1" s="65" t="inlineStr">
-        <is>
-          <t>설계</t>
-        </is>
-      </c>
       <c r="H1" s="65" t="inlineStr">
         <is>
-          <t>사용</t>
+          <t>근거(A)</t>
+        </is>
+      </c>
+      <c r="I1" s="65" t="inlineStr">
+        <is>
+          <t>근거(B)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1624</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T1≡2</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>针刺研究 46(1) (DB 표기: World Journal of Acupuncture-Moxibustion)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>关于悬钟穴定位的探讨 / Location of acupoint Xuanzhong (GB39) — 刘佳男 등</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.13702/j.1000-0607.200282 (본문 PDF)</t>
+          <t>B1-01, B1-03, B1-06, B2-09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>문헌 연구(정위)</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>T1 정위 근거(胫骨前嵴与腓骨前缘之间), 박동 촉지 곤란 지적</t>
+          <t>전경골동·정맥 + 깊은종아리신경은 규범 해부서와 2대 교재(전경골동맥 등재)로 확인되나 T1 위치 특이 실측(B2 영상·사체)이 없어 1.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>T1 실체 = 전경골동맥+심비골신경(L4-L5)이라는 해석은 규범 해부와 통감·통고 해석으로 지지되나 혈위 특이 심도 실측 없음, 1624는 박동 촉지 곤란을 지적 → 1</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1610</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T1≡2</t>
+        </is>
       </c>
       <c r="B3" t="n">
-        <v>2003</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>대한침구학회지</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>치매와 관련된 뇌영역에 투사되는 경혈(SJ5·PC6·SP6·GB39)의 신경해부학적 연구</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>동물 신경추적</t>
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>B1-03, B3-05</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>T2 B-Check ④</t>
+          <t>깊은종아리신경 L4~L5(S1) 근절·피절 vs 《明堂》 원주치 표적(위, T6~T9 내장절) 분절 불일치. 하지 자극의 위운동 조절은 상척수성(미주) 체성-자율 반사로 설명되는 유추 수준 → 1.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>심비골신경 L4-L5(피절 L5) vs 원 주치 위장(腹满·胃中有热·不嗜食, 내장절 T6-T9/미주) 분절 불일치; 하지-위 반사는 상척수(미주) 경로로만 연결되는 유추 → 1</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1612</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T1≡2</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>2006</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>대한한의학회지</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>양릉천-현종 전침치료가 뇌경색환자 및 정상인의 뇌혈류에 미치는 영향</t>
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>B3-05, B3-06, B3-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인체 비RCT(배혈)</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>T2 B-Check ④⑥</t>
+          <t>깊은종아리신경 심부 근육 구심(group III/IV, Aδ/C) 관여는 ST36-37 등 타 경혈·마취 동물에서 검증된 범위 밖 유추 → 1.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>심부 근·혈관주위 Ⅲ/Ⅳ군·Aβ/Aδ 구심섬유는 마취 동물 일반 기전, T1 미검증 범위 밖 → 1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1615</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T1≡2</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>대한침구의학회지</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>懸鍾(GB39)·陽陵泉(GB34)의 電鍼 및 레이저침이 白鼠의 神經病理性 疼痛에 미치는 영향</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.13045/acupunct.2013012</t>
+          <t>B3-05, B3-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>동물(배혈)</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>T2 B-Check ③⑤</t>
+          <t>후지 체성자극 → 연수(rVLM/NTS·미주 운동핵) 경로는 마취 쥐·고양이, 타 경혈 근거 → 1.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>후지 자극→상척수 미주/rVLM 경로는 동물·타 부위(비골신경 전침) 근거 유추</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>1903</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T1≡2</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Zhen Ci Yan Jiu</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Electroacupuncture at "Zusanli"(ST36) and "Xuanzhong"(GB39) improves inflammatory reactions…</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>31532135</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.13702/j.1000-0607.180555</t>
+          <t>B3-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>동물(배혈)</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>T2 B-Check ⑤</t>
+          <t>원주치 '腹满·胃中有热·不嗜食'과 하지 자극의 미주성 위운동 촉진 방향은 마취 쥐 일반 기전으로 유추 가능하나 T1 특이 근거 없음 → 1.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>마취 쥐 후지 체성 자극의 위운동 미주성 촉진 반사가 원 주치(위 병증) 방향과 개념상 부합하나 T1 직접 근거 없음; 1904는 위팽만 심혈관반사 지표로 위 기능 효과 아님</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>1902</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T1≡2</t>
+        </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Zhongguo Zhen Jiu</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Electroacupuncture for the prevention of chemotherapy-induced peripheral neuropathy: an RCT</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>39658376</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.13703/j.0255-2930.20240222-k0001</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>인체 RCT(다혈위)</t>
+          <t>B4-05</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>T2 B-Check ⑥</t>
+          <t>T1 위치 자침의 인체 신경영상·자율신경 지표·임상 연구 없음. 혈위 특이성 논쟁(B4-05) 미해결 → 0.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>T1 정위로 자침한 인체 생리·임상 연구 없음</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>1904</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2002</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Am J Physiol Regul Integr Comp Physiol</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Effect of electroacupuncture on pressor reflex during gastric distension</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>12388466</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>10.1152/ajpregu.00192.2002</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>동물</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T1≡2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>T1 B-Check ③~⑤ 유추</t>
+          <t>미부합 → 반사 기전 가설</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>1620</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
       </c>
       <c r="B9" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>针灸临床杂志</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>髓会绝骨的文献研究及临床应用概论</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>문헌 연구</t>
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>B1-01, B1-03, B2-09</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>참고(불산입)</t>
+          <t>얕은·깊은종아리신경, 앞정강동정맥, 폄근군은 규범 해부·2대 교재로 확인되나 GB39 특이 영상·사체 실측 논문 없음(B2 2점 조건 미충족). 보고서의 '비골동맥 관통지=動脈中' 주장은 《通考》의 앞정강동맥 해석과 불일치.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>교재 2종이 얕은·깊은종아리신경과 앞정강동맥을 지정하지만 혈관 구성이 서로 다르고 혈위 특이 영상 실측(B2-10 유형)이 없음. 보고서의 '비골동맥 관통지=動脈' 동정은 通考와 상충함.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>불산입: 1842·1905·1845·1922(종설·데이터마이닝), 1910·1915·1924·1925·1911(GB39 포함/단독성 미확인), 1913(GB39 실측 아님)</t>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>B1-03, B3-05, B3-20</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L4~S1 피절·근절은 국소 주치(下肢痿痺·足脛痛)와 정합. 보고서의 'L4-S1→C3-C5 체성-체성 이완 반사'(頸項强痛)는 분절 근거 없음. 명당경 원주치(위병, T6~T9)와도 분절 불일치.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>L4~S1 피절·근절은 국소 하지 주치(下肢痿痺·足脛痛)와 맞음. 원전 단독 주치인 腹滿·胃中有熱·不嗜食(위 T6~T9)과 보고서가 주장한 頸項强痛(C3~C5)은 분절이 불일치하여 상척수성 유추만 가능함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>B3-04, B3-06, B3-11, B3-17</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>침 자극 구심 섬유(Aδ/C) 일반 틀과 GB39·GB34 전침 진통 동물 연구(복합 혈위)만 존재 — 유추·동물 한정.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>구심 섬유형에 관한 일반 기전과 하지 심부 근막 PROKR2 기전(ST36 검증)은 범위 밖이므로 유추로만 인정함. GB39 고유의 섬유형 연구는 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>B3-05, B3-07, B3-11</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1610, 1612</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>GB39 관련 뇌영역 투사 추적(동물), GB34-GB39 전침 뇌혈류 변화(인체, 복합 혈위)로 중추 관여는 간접 시사. 경로 특정 근거 없음.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>GB39 신경추적 연구(1610, 동물)와 진통 중추 경로에 관한 일반 기전뿐임. 보고서의 'C3-C5 분절 상행 반사'는 근거가 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>B3-05, B3-11, B3-16</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1615, 1903</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>국소 진통·항염 방향은 하지 통증 주치와 동물 수준에서 부합. 頸項强痛 원격 효과·髓會(골수) 효과의 원심 경로 근거 없음.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>사지 자극이 위 운동과 염증을 조절한다는 기전은 마취 쥐·마우스 ST36에서 나온 유추이고, ST36+GB39 병용 동물 연구(1903)가 있음. 고전 주치(위열·복만)의 효과 방향과 직접 대응하는 GB39 연구는 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>B4-03, B4-04, B4-05</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1612, 1902</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>인체 근거는 복합 혈위 전침(뇌혈류 비RCT, CIPN RCT)뿐으로 GB39 특이 전환 근거 아님. B4-04·B4-05의 혈위 비특이성 반증 병기 필요.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>GB34-GB39 전침 인체 뇌혈류 연구(비RCT, 배혈)가 1편 있음. 혈위 특이성 반증(B4-04·B4-05)을 함께 고려해 1점.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>미부합 → 반사 기전 가설</t>
         </is>
       </c>
     </row>
